--- a/other_files/汇兴-增鑫API数据接入/网关数据.xlsx
+++ b/other_files/汇兴-增鑫API数据接入/网关数据.xlsx
@@ -4,12 +4,12 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="11730" windowHeight="9370"/>
+    <workbookView windowWidth="14320" windowHeight="12800" activeTab="2"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
-    <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
-    <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="栏舍编号" sheetId="1" r:id="rId1"/>
+    <sheet name="字段表" sheetId="2" r:id="rId2"/>
+    <sheet name="配置字段" sheetId="7" r:id="rId3"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="52" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="153">
   <si>
     <r>
       <rPr>
@@ -49,62 +49,1120 @@
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
+      <t>楼舍</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>网关编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>网关上报地址</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>楼舍</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>id</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（？）</t>
+    </r>
+  </si>
+  <si>
+    <t>unitName</t>
+  </si>
+  <si>
+    <t>gatewayNo</t>
+  </si>
+  <si>
+    <t>gatewayIp</t>
+  </si>
+  <si>
+    <t>unitId</t>
+  </si>
+  <si>
+    <r>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>栋</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2023092836</t>
+  </si>
+  <si>
+    <t>39.165.19.84</t>
+  </si>
+  <si>
+    <t>40a6fc2e64859dad66cf87057c76ad9e</t>
+  </si>
+  <si>
+    <r>
+      <t>2-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2023120402</t>
+  </si>
+  <si>
+    <t>47.97.125.216</t>
+  </si>
+  <si>
+    <t>e712a7dd9912b3dd328ebeab531dc543</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可以共用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ip</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041507</t>
+  </si>
+  <si>
+    <t>90cba802405352409a87df035cc776b0</t>
+  </si>
+  <si>
+    <r>
+      <t>2-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041511</t>
+  </si>
+  <si>
+    <t>10.147.0.118</t>
+  </si>
+  <si>
+    <t>41cd1a45d1c5c881e3d110d26258fa00</t>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>栋</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>3-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024090302</t>
+  </si>
+  <si>
+    <t>1cf314e8c706a303cdfce55d0ba8825c</t>
+  </si>
+  <si>
+    <r>
+      <t>3-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2023120448</t>
+  </si>
+  <si>
+    <t>1c5072528e1efc9e7d4b68503fd52704</t>
+  </si>
+  <si>
+    <r>
+      <t>3-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041504</t>
+  </si>
+  <si>
+    <t>e838146c63828cce106a4983ef93aee8</t>
+  </si>
+  <si>
+    <r>
+      <t>3-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041509</t>
+  </si>
+  <si>
+    <t>86ff056dd242c133ca7173a07f53333d</t>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>栋</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>4-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041508</t>
+  </si>
+  <si>
+    <t>4b4469efe50237d4207d60f79b1a56aa</t>
+  </si>
+  <si>
+    <r>
+      <t>4-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041502</t>
+  </si>
+  <si>
+    <t>551b9bdc9a95fa2a4c2d1fb924aa4859</t>
+  </si>
+  <si>
+    <r>
+      <t>4-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041505</t>
+  </si>
+  <si>
+    <t>eb0f5c4d9a5b397ff30b0d1f7f2d0100</t>
+  </si>
+  <si>
+    <r>
+      <t>4-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041506</t>
+  </si>
+  <si>
+    <t>e65f1ebafe2787cec95df5e685a511d9</t>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>栋</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>/</t>
+  </si>
+  <si>
+    <t>10c42ed81b5f40cfbc568f35dbae4a8e</t>
+  </si>
+  <si>
+    <r>
+      <t>5-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>d537e9b2b5634e898908f02025df0e6a</t>
+  </si>
+  <si>
+    <r>
+      <t>5-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041503</t>
+  </si>
+  <si>
+    <t>8a1b5538dd9e0266c60d32b3d2f5a50b</t>
+  </si>
+  <si>
+    <r>
+      <t>5-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>7c44240126a240c087f91a0890fba4f8</t>
+  </si>
+  <si>
+    <r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>栋</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>6-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2023120430</t>
+  </si>
+  <si>
+    <t>41c897cadfa52eeaf42149ff2b550daa</t>
+  </si>
+  <si>
+    <r>
+      <t>6-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2025102103</t>
+  </si>
+  <si>
+    <t>64ba729f187eabcf1ae4b6d66f96145e</t>
+  </si>
+  <si>
+    <r>
+      <t>6-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2023120447</t>
+  </si>
+  <si>
+    <t>0099d2a09dbc98294ab356c8dc8f52f3</t>
+  </si>
+  <si>
+    <r>
+      <t>6-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024081602</t>
+  </si>
+  <si>
+    <t>b667fb650620892a4d67ebe8ac8dc9a8</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>参数名</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>解释</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>类型</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>示例值（字段具体值）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>备注</t>
+    </r>
+  </si>
+  <si>
+    <t>areaId</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>区域</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> id</t>
+    </r>
+  </si>
+  <si>
+    <t>String</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？是否可以通过饲喂器异常数据及时发现网关异常</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>or</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>及时纠偏（之前出现过日龄丢失两天，但是传感器数据的日龄显示是连续的）</t>
+    </r>
+  </si>
+  <si>
+    <t>areaNo</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>区域编号</t>
+    </r>
+  </si>
+  <si>
+    <t>string</t>
+  </si>
+  <si>
+    <t>"1"</t>
+  </si>
+  <si>
+    <t>AuthorizationF</t>
+  </si>
+  <si>
+    <t>Header</t>
+  </si>
+  <si>
+    <t>Bearer expogDjofnFGuhuvbufi</t>
+  </si>
+  <si>
+    <t>dayOld</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>总日龄</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>不可信；目前二栋转舍天数大于总日龄</t>
+    </r>
+  </si>
+  <si>
+    <t>fdQrcode</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>饲喂器二维码</t>
+    </r>
+  </si>
+  <si>
+    <t>integer(int32)</t>
+  </si>
+  <si>
+    <t>170B10004A</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>同上字段</t>
+    </r>
+  </si>
+  <si>
+    <t>fenceNum</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>栏号</t>
+    </r>
+  </si>
+  <si>
+    <t>1-28</t>
+  </si>
+  <si>
+    <t>forceFood</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>强制下料量</t>
+    </r>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>forceWater</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>强制下水</t>
+    </r>
+  </si>
+  <si>
+    <t>30</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>网关编号</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>部分问题总结</t>
+    </r>
+  </si>
+  <si>
+    <t>getwayId</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>网关</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> id</t>
+    </r>
+  </si>
+  <si>
+    <t>array</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>服务协议的</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>API</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>请求参数的必选类型不正确</t>
+    </r>
+  </si>
+  <si>
+    <t>intDwWeight</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当天实际饮水量</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>_L</t>
+    </r>
+  </si>
+  <si>
+    <t>intFdWeight</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>当天实际饲喂量</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>36</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（系统显示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>0.36</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单位有问题，底层原值</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>36</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>，显示</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve">0.36kg
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>应该是累计值</t>
+    </r>
+  </si>
+  <si>
+    <t>lairagDayold</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>转舍天数</t>
+    </r>
+  </si>
+  <si>
+    <t>lsId</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t>栏舍</t>
     </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>网关编号</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>网关区域编号</t>
-    </r>
-  </si>
-  <si>
-    <t>unitName</t>
-  </si>
-  <si>
-    <t>gatewayNo</t>
-  </si>
-  <si>
-    <t>areaNo</t>
-  </si>
-  <si>
-    <r>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>栋</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>2-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> id / </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>二维码</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>楼宇</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>id</t>
+    </r>
+  </si>
+  <si>
+    <t>lsName</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>栏舍名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>栋育肥舍</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>楼宇名称</t>
+    </r>
+  </si>
+  <si>
+    <t>pigletNum</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？（最大）猪只个数</t>
+    </r>
+  </si>
+  <si>
+    <t>qrcode</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>饲喂器编码</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元名称</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
@@ -112,380 +1170,153 @@
     </r>
   </si>
   <si>
-    <t>XH2023092836</t>
-  </si>
-  <si>
-    <r>
-      <t>2-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
+    <r>
+      <rPr>
+        <sz val="16"/>
         <rFont val="黑体"/>
         <charset val="134"/>
       </rPr>
       <t>单元</t>
     </r>
-  </si>
-  <si>
-    <t>XH2023120402</t>
-  </si>
-  <si>
-    <r>
-      <t>2-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024041507</t>
-  </si>
-  <si>
-    <r>
-      <t>2-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024041511</t>
-  </si>
-  <si>
-    <r>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>栋</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>3-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024090302</t>
-  </si>
-  <si>
-    <r>
-      <t>3-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2023120448</t>
-  </si>
-  <si>
-    <r>
-      <t>3-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024041504</t>
-  </si>
-  <si>
-    <r>
-      <t>3-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024041509</t>
-  </si>
-  <si>
-    <r>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>栋</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>4-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024041508</t>
-  </si>
-  <si>
-    <r>
-      <t>4-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024041502</t>
-  </si>
-  <si>
-    <r>
-      <t>4-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024041505</t>
-  </si>
-  <si>
-    <r>
-      <t>4-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024041506</t>
-  </si>
-  <si>
-    <r>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>栋</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>5-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>/</t>
-  </si>
-  <si>
-    <r>
-      <t>5-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>5-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024041503</t>
-  </si>
-  <si>
-    <r>
-      <t>5-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>栋</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>6-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2023120430</t>
-  </si>
-  <si>
-    <r>
-      <t>6-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2025102103</t>
-  </si>
-  <si>
-    <r>
-      <t>6-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2023120447</t>
-  </si>
-  <si>
-    <r>
-      <t>6-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2024081602</t>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ID</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>网关</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>ip</t>
+    </r>
+  </si>
+  <si>
+    <t>farmId</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>猪场</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> id</t>
+    </r>
+  </si>
+  <si>
+    <t>91e59e22666028fb7da2105756c17d28</t>
+  </si>
+  <si>
+    <t>参数名</t>
+  </si>
+  <si>
+    <t>参数解释</t>
+  </si>
+  <si>
+    <t>类型</t>
+  </si>
+  <si>
+    <t>取值</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <r>
+      <t>猪场</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>汇兴全场唯一</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>farm id</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>但是在</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>5.2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>调用时显示不存在</t>
+    </r>
+  </si>
+  <si>
+    <t>网关区域编号</t>
+  </si>
+  <si>
+    <t>唯一</t>
+  </si>
+  <si>
+    <t>areaID</t>
+  </si>
+  <si>
+    <r>
+      <t>区域</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t xml:space="preserve"> id</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -498,7 +1329,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="23">
+  <fonts count="29">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -507,8 +1338,30 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <color theme="1"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="16"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <name val="Arial"/>
       <charset val="134"/>
     </font>
@@ -668,6 +1521,16 @@
       <name val="黑体"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="16"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -989,147 +1852,189 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="2">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1443,214 +2348,369 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="3"/>
+  <dimension ref="A1:H33"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.81818181818182" style="1" customWidth="1"/>
-    <col min="2" max="2" width="12" style="1" customWidth="1"/>
-    <col min="3" max="3" width="19.7272727272727" style="1" customWidth="1"/>
-    <col min="4" max="16384" width="9" style="1"/>
+    <col min="1" max="1" width="6.81818181818182" style="16" customWidth="1"/>
+    <col min="2" max="2" width="12" style="16" customWidth="1"/>
+    <col min="3" max="3" width="15.9090909090909" style="16" customWidth="1"/>
+    <col min="4" max="4" width="15.6363636363636" style="16" customWidth="1"/>
+    <col min="5" max="5" width="17.7272727272727" style="16" customWidth="1"/>
+    <col min="6" max="6" width="10.9090909090909" style="16" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="16"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4">
-      <c r="A1" s="2" t="s">
+    <row r="1" s="16" customFormat="1" spans="1:8">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="16" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-    </row>
-    <row r="2" spans="1:4">
-      <c r="B2" s="1" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="3" t="s">
+      <c r="F1" s="6"/>
+    </row>
+    <row r="2" spans="1:8">
+      <c r="B2" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="C2" s="15" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="2" t="s">
+      <c r="D2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="E2" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="F2" s="6"/>
+    </row>
+    <row r="3" spans="1:8">
+      <c r="A3" s="16" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="4" spans="1:4">
-      <c r="B4" s="2" t="s">
+      <c r="B3" s="16" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C3" s="15" t="s">
         <v>11</v>
       </c>
-    </row>
-    <row r="5" spans="1:4">
-      <c r="B5" s="2" t="s">
+      <c r="D3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="E3" s="16" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:4">
-      <c r="B6" s="2" t="s">
+    <row r="4" spans="1:8">
+      <c r="B4" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="3" t="s">
+      <c r="C4" s="15" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="2" t="s">
+      <c r="D4" s="17" t="s">
         <v>16</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="E4" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="C8" s="3" t="s">
+      <c r="H4" s="16" t="s">
         <v>18</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="B9" s="2" t="s">
+    <row r="5" spans="1:8">
+      <c r="B5" s="16" t="s">
         <v>19</v>
       </c>
-      <c r="C9" s="3" t="s">
+      <c r="C5" s="15" t="s">
         <v>20</v>
       </c>
-    </row>
-    <row r="10" spans="1:4">
-      <c r="B10" s="2" t="s">
+      <c r="D5" s="17" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="16" t="s">
         <v>21</v>
       </c>
-      <c r="C10" s="3" t="s">
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="16" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="11" spans="1:4">
-      <c r="B11" s="2" t="s">
+      <c r="C6" s="15" t="s">
         <v>23</v>
       </c>
-      <c r="C11" s="3" t="s">
+      <c r="D6" s="16" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="2" t="s">
+      <c r="E6" s="16" t="s">
         <v>25</v>
       </c>
-      <c r="B13" s="2" t="s">
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="16" t="s">
         <v>26</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="B8" s="16" t="s">
         <v>27</v>
       </c>
-    </row>
-    <row r="14" spans="1:4">
-      <c r="B14" s="2" t="s">
+      <c r="C8" s="15" t="s">
         <v>28</v>
       </c>
-      <c r="C14" s="3" t="s">
+      <c r="D8" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E8" s="16" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="B15" s="2" t="s">
+    <row r="9" spans="1:8">
+      <c r="B9" s="16" t="s">
         <v>30</v>
       </c>
-      <c r="C15" s="3" t="s">
+      <c r="C9" s="15" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="16" spans="1:4">
-      <c r="B16" s="2" t="s">
+      <c r="D9" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E9" s="16" t="s">
         <v>32</v>
       </c>
-      <c r="C16" s="3" t="s">
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" s="16" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:3">
-      <c r="A18" s="2" t="s">
+      <c r="C10" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="B18" s="2" t="s">
+      <c r="D10" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E10" s="16" t="s">
         <v>35</v>
       </c>
-      <c r="C18" s="2" t="s">
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" s="16" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="19" spans="1:3">
-      <c r="B19" s="2" t="s">
+      <c r="C11" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="C19" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="20" spans="1:3">
-      <c r="B20" s="2" t="s">
+      <c r="D11" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E11" s="16" t="s">
         <v>38</v>
       </c>
-      <c r="C20" s="3" t="s">
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="16" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="21" spans="1:3">
-      <c r="B21" s="2" t="s">
+      <c r="B13" s="16" t="s">
         <v>40</v>
       </c>
-      <c r="C21" s="2" t="s">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="23" spans="1:3">
-      <c r="A23" s="2" t="s">
+      <c r="C13" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="B23" s="2" t="s">
+      <c r="D13" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E13" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="C23" s="3" t="s">
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14" s="16" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="24" spans="1:3">
-      <c r="B24" s="2" t="s">
+      <c r="C14" s="15" t="s">
         <v>44</v>
       </c>
-      <c r="C24" s="3" t="s">
+      <c r="D14" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E14" s="16" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="25" spans="1:3">
-      <c r="B25" s="2" t="s">
+    <row r="15" spans="1:8">
+      <c r="B15" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C25" s="3" t="s">
+      <c r="C15" s="15" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="26" spans="1:3">
-      <c r="B26" s="2" t="s">
+      <c r="D15" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C26" s="3" t="s">
+    </row>
+    <row r="16" spans="1:8">
+      <c r="B16" s="16" t="s">
         <v>49</v>
       </c>
+      <c r="C16" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E16" s="16" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="B18" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C18" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E18" s="16" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="B19" s="16" t="s">
+        <v>56</v>
+      </c>
+      <c r="C19" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E19" s="16" t="s">
+        <v>57</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5">
+      <c r="B20" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C20" s="15" t="s">
+        <v>59</v>
+      </c>
+      <c r="D20" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E20" s="16" t="s">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5">
+      <c r="B21" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="C21" s="16" t="s">
+        <v>54</v>
+      </c>
+      <c r="E21" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5">
+      <c r="A23" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="B23" s="16" t="s">
+        <v>64</v>
+      </c>
+      <c r="C23" s="15" t="s">
+        <v>65</v>
+      </c>
+      <c r="D23" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E23" s="16" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5">
+      <c r="B24" s="16" t="s">
+        <v>67</v>
+      </c>
+      <c r="C24" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="D24" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E24" s="16" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5">
+      <c r="B25" s="16" t="s">
+        <v>70</v>
+      </c>
+      <c r="C25" s="15" t="s">
+        <v>71</v>
+      </c>
+      <c r="D25" s="15" t="s">
+        <v>12</v>
+      </c>
+      <c r="E25" s="16" t="s">
+        <v>72</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5">
+      <c r="B26" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="C26" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="D26" s="15" t="s">
+        <v>16</v>
+      </c>
+      <c r="E26" s="16" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5">
+      <c r="A28" s="6"/>
+      <c r="B28" s="6"/>
+      <c r="C28" s="6"/>
+    </row>
+    <row r="29" spans="1:5">
+      <c r="A29" s="6"/>
+      <c r="B29" s="6"/>
+      <c r="C29" s="6"/>
+    </row>
+    <row r="30" spans="1:5">
+      <c r="A30" s="6"/>
+      <c r="B30" s="6"/>
+      <c r="C30" s="6"/>
+    </row>
+    <row r="31" spans="1:5">
+      <c r="A31" s="6"/>
+      <c r="B31" s="6"/>
+      <c r="C31" s="6"/>
+    </row>
+    <row r="32" spans="1:5">
+      <c r="A32" s="6"/>
+      <c r="B32" s="6"/>
+      <c r="C32" s="6"/>
+    </row>
+    <row r="33" spans="1:3">
+      <c r="A33" s="6"/>
+      <c r="B33" s="6"/>
+      <c r="C33" s="6"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1662,9 +2722,315 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
+  <dimension ref="A1:K22"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="20"/>
+  <cols>
+    <col min="1" max="1" width="20.5454545454545" style="4" customWidth="1"/>
+    <col min="2" max="2" width="25.8181818181818" style="4" customWidth="1"/>
+    <col min="3" max="3" width="18.1818181818182" style="4" customWidth="1"/>
+    <col min="4" max="4" width="27.8181818181818" style="5" customWidth="1"/>
+    <col min="5" max="5" width="17.6363636363636" style="4" customWidth="1"/>
+    <col min="6" max="7" width="9" style="6"/>
+    <col min="8" max="16384" width="9" style="7"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" spans="1:11">
+      <c r="A1" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="B1" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="C1" s="4" t="s">
+        <v>78</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="E1" s="4" t="s">
+        <v>80</v>
+      </c>
+    </row>
+    <row r="2" ht="21" spans="1:11">
+      <c r="A2" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D2" s="5">
+        <v>1</v>
+      </c>
+      <c r="K2" s="7" t="s">
+        <v>84</v>
+      </c>
+    </row>
+    <row r="3" ht="21" spans="1:11">
+      <c r="A3" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11">
+      <c r="A4" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="B4" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="5" ht="21" spans="1:11">
+      <c r="A5" s="4" t="s">
+        <v>92</v>
+      </c>
+      <c r="B5" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="E5" s="4" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="6" ht="21" spans="1:11">
+      <c r="A6" s="4" t="s">
+        <v>95</v>
+      </c>
+      <c r="B6" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>98</v>
+      </c>
+      <c r="E6" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="7" ht="21" spans="1:11">
+      <c r="A7" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="B7" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>102</v>
+      </c>
+    </row>
+    <row r="8" ht="21" spans="1:11">
+      <c r="A8" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="B8" s="4" t="s">
+        <v>104</v>
+      </c>
+      <c r="D8" s="5" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="9" ht="21" spans="1:11">
+      <c r="A9" s="4" t="s">
+        <v>106</v>
+      </c>
+      <c r="B9" s="4" t="s">
+        <v>107</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="10" ht="21" spans="1:11">
+      <c r="A10" s="4" t="s">
+        <v>6</v>
+      </c>
+      <c r="B10" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C10" s="8" t="s">
+        <v>87</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="K10" s="7" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="11" ht="21" spans="1:11">
+      <c r="A11" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>113</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>11</v>
+      </c>
+      <c r="E11" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="K11" s="7" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="12" ht="21" spans="1:11">
+      <c r="A12" s="4" t="s">
+        <v>115</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>116</v>
+      </c>
+      <c r="F12" s="10"/>
+    </row>
+    <row r="13" ht="23" customHeight="1" spans="1:11">
+      <c r="A13" s="4" t="s">
+        <v>117</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>118</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="E13" s="11" t="s">
+        <v>120</v>
+      </c>
+      <c r="G13" s="12"/>
+    </row>
+    <row r="14" ht="21" spans="1:11">
+      <c r="A14" s="4" t="s">
+        <v>121</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="15" ht="21" spans="1:11">
+      <c r="A15" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>124</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="E15" s="4" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="16" ht="21" spans="1:11">
+      <c r="A16" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>127</v>
+      </c>
+      <c r="D16" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="E16" s="4" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="17" ht="21" spans="1:4">
+      <c r="A17" s="4" t="s">
+        <v>130</v>
+      </c>
+      <c r="B17" s="4" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="18" ht="21" spans="1:4">
+      <c r="A18" s="4" t="s">
+        <v>132</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D18" s="5" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="19" ht="21" spans="1:4">
+      <c r="A19" s="4" t="s">
+        <v>5</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="13"/>
+      <c r="D19" s="14" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="20" ht="21" spans="1:4">
+      <c r="A20" s="4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="5" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="21" ht="21" spans="1:4">
+      <c r="A21" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>137</v>
+      </c>
+      <c r="D21" s="15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" ht="21" spans="1:4">
+      <c r="A22" s="4" t="s">
+        <v>138</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D22" s="5" t="s">
+        <v>140</v>
+      </c>
+    </row>
+  </sheetData>
+  <sortState ref="A2:K18">
+    <sortCondition ref="A2:A18"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <headerFooter/>
@@ -1674,11 +3040,77 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14"/>
-  <sheetData/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
+  <dimension ref="A1:F4"/>
+  <sheetFormatPr defaultColWidth="11.9090909090909" defaultRowHeight="20" outlineLevelRow="3" outlineLevelCol="5"/>
+  <cols>
+    <col min="1" max="1" width="11.9090909090909" style="1" customWidth="1"/>
+    <col min="2" max="2" width="18.9090909090909" style="1" customWidth="1"/>
+    <col min="3" max="3" width="11.9090909090909" style="1" customWidth="1"/>
+    <col min="4" max="4" width="18.2727272727273" style="1" customWidth="1"/>
+    <col min="5" max="16384" width="11.9090909090909" style="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="21" spans="1:6">
+      <c r="A1" s="2" t="s">
+        <v>141</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="2" ht="21" spans="1:6">
+      <c r="A2" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>146</v>
+      </c>
+      <c r="C2" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D2" s="3" t="s">
+        <v>140</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="F2" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="3" ht="21" spans="1:6">
+      <c r="A3" s="3" t="s">
+        <v>85</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>149</v>
+      </c>
+      <c r="D3" s="1">
+        <v>1</v>
+      </c>
+      <c r="E3" s="2" t="s">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="4" ht="21" spans="1:6">
+      <c r="A4" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
 </file>
--- a/other_files/汇兴-增鑫API数据接入/网关数据.xlsx
+++ b/other_files/汇兴-增鑫API数据接入/网关数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="14320" windowHeight="12800" activeTab="2"/>
+    <workbookView windowWidth="25600" windowHeight="12790"/>
   </bookViews>
   <sheets>
     <sheet name="栏舍编号" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="189" uniqueCount="153">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="154">
   <si>
     <r>
       <rPr>
@@ -104,6 +104,9 @@
     </r>
   </si>
   <si>
+    <t>区域id</t>
+  </si>
+  <si>
     <t>unitName</t>
   </si>
   <si>
@@ -116,7 +119,16 @@
     <t>unitId</t>
   </si>
   <si>
-    <r>
+    <t>areaId</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>2</t>
     </r>
     <r>
@@ -131,6 +143,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>2-1</t>
     </r>
     <r>
@@ -154,6 +172,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>2-2</t>
     </r>
     <r>
@@ -206,6 +230,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>2-3</t>
     </r>
     <r>
@@ -226,6 +256,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>2-4</t>
     </r>
     <r>
@@ -249,6 +285,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>3</t>
     </r>
     <r>
@@ -263,6 +305,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>3-1</t>
     </r>
     <r>
@@ -283,6 +331,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>3-2</t>
     </r>
     <r>
@@ -303,6 +357,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>3-3</t>
     </r>
     <r>
@@ -323,6 +383,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>3-4</t>
     </r>
     <r>
@@ -343,6 +409,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>4</t>
     </r>
     <r>
@@ -357,6 +429,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>4-1</t>
     </r>
     <r>
@@ -377,6 +455,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>4-2</t>
     </r>
     <r>
@@ -397,6 +481,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>4-3</t>
     </r>
     <r>
@@ -417,6 +507,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>4-4</t>
     </r>
     <r>
@@ -437,6 +533,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>5</t>
     </r>
     <r>
@@ -451,6 +553,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>5-1</t>
     </r>
     <r>
@@ -471,6 +579,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>5-2</t>
     </r>
     <r>
@@ -488,6 +602,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>5-3</t>
     </r>
     <r>
@@ -508,6 +628,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>5-4</t>
     </r>
     <r>
@@ -525,6 +651,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>6</t>
     </r>
     <r>
@@ -539,6 +671,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>6-1</t>
     </r>
     <r>
@@ -559,6 +697,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>6-2</t>
     </r>
     <r>
@@ -579,6 +723,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>6-3</t>
     </r>
     <r>
@@ -599,6 +749,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>6-4</t>
     </r>
     <r>
@@ -668,9 +824,6 @@
     </r>
   </si>
   <si>
-    <t>areaId</t>
-  </si>
-  <si>
     <r>
       <rPr>
         <sz val="16"/>
@@ -951,6 +1104,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>36</t>
     </r>
     <r>
@@ -980,6 +1138,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>?</t>
     </r>
     <r>
@@ -1099,6 +1262,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>5</t>
     </r>
     <r>
@@ -1158,6 +1326,11 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
       <t>1</t>
     </r>
     <r>
@@ -1246,6 +1419,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t>猪场</t>
     </r>
     <r>
@@ -1260,6 +1439,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t>汇兴全场唯一</t>
     </r>
     <r>
@@ -1274,6 +1459,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t>但是在</t>
     </r>
     <r>
@@ -1306,6 +1497,12 @@
   </si>
   <si>
     <r>
+      <rPr>
+        <sz val="16"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
       <t>区域</t>
     </r>
     <r>
@@ -1329,7 +1526,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="29">
+  <fonts count="30">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1369,6 +1566,12 @@
       <sz val="10.5"/>
       <color theme="1"/>
       <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1522,12 +1725,12 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="16"/>
+      <sz val="11"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="16"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
@@ -1852,137 +2055,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -1990,9 +2193,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -2031,7 +2231,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
@@ -2348,369 +2548,343 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:H33"/>
+  <dimension ref="A1:H26"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.81818181818182" style="16" customWidth="1"/>
-    <col min="2" max="2" width="12" style="16" customWidth="1"/>
-    <col min="3" max="3" width="15.9090909090909" style="16" customWidth="1"/>
-    <col min="4" max="4" width="15.6363636363636" style="16" customWidth="1"/>
-    <col min="5" max="5" width="17.7272727272727" style="16" customWidth="1"/>
-    <col min="6" max="6" width="10.9090909090909" style="16" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="16"/>
+    <col min="1" max="1" width="6.81818181818182" style="5" customWidth="1"/>
+    <col min="2" max="2" width="12" style="5" customWidth="1"/>
+    <col min="3" max="3" width="15.9090909090909" style="5" customWidth="1"/>
+    <col min="4" max="4" width="15.6363636363636" style="5" customWidth="1"/>
+    <col min="5" max="5" width="34.5454545454545" style="5" customWidth="1"/>
+    <col min="6" max="6" width="25.0909090909091" style="5" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" s="16" customFormat="1" spans="1:8">
-      <c r="A1" s="16" t="s">
+    <row r="1" s="5" customFormat="1" spans="1:8">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="16" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="16" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="16" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="6"/>
+      <c r="F1" s="15" t="s">
+        <v>5</v>
+      </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="B2" s="16" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="15" t="s">
+      <c r="B2" s="5" t="s">
         <v>6</v>
       </c>
-      <c r="D2" s="16" t="s">
+      <c r="C2" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="16" t="s">
+      <c r="D2" s="5" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="6"/>
+      <c r="E2" s="5" t="s">
+        <v>9</v>
+      </c>
+      <c r="F2" s="5" t="s">
+        <v>10</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" s="16" t="s">
-        <v>10</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="A3" s="5" t="s">
         <v>11</v>
       </c>
-      <c r="D3" s="15" t="s">
+      <c r="B3" s="5" t="s">
         <v>12</v>
       </c>
-      <c r="E3" s="16" t="s">
+      <c r="C3" s="14" t="s">
         <v>13</v>
       </c>
+      <c r="D3" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E3" s="5" t="s">
+        <v>15</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="B4" s="16" t="s">
+      <c r="B4" s="5" t="s">
+        <v>16</v>
+      </c>
+      <c r="C4" s="14" t="s">
+        <v>17</v>
+      </c>
+      <c r="D4" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8">
+      <c r="B5" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="C5" s="14" t="s">
+        <v>22</v>
+      </c>
+      <c r="D5" s="16" t="s">
+        <v>18</v>
+      </c>
+      <c r="E5" s="5" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8">
+      <c r="B6" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="C6" s="14" t="s">
+        <v>25</v>
+      </c>
+      <c r="D6" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="E6" s="5" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8">
+      <c r="A8" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="B8" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="C8" s="14" t="s">
+        <v>30</v>
+      </c>
+      <c r="D8" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E8" s="5" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8">
+      <c r="B9" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C9" s="14" t="s">
+        <v>33</v>
+      </c>
+      <c r="D9" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E9" s="5" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8">
+      <c r="B10" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="C10" s="14" t="s">
+        <v>36</v>
+      </c>
+      <c r="D10" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E10" s="5" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8">
+      <c r="B11" s="5" t="s">
+        <v>38</v>
+      </c>
+      <c r="C11" s="14" t="s">
+        <v>39</v>
+      </c>
+      <c r="D11" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E11" s="5" t="s">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8">
+      <c r="A13" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="B13" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="14" t="s">
+        <v>43</v>
+      </c>
+      <c r="D13" s="14" t="s">
         <v>14</v>
       </c>
-      <c r="C4" s="15" t="s">
-        <v>15</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E4" s="16" t="s">
-        <v>17</v>
-      </c>
-      <c r="H4" s="16" t="s">
+      <c r="E13" s="5" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8">
+      <c r="B14" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="C14" s="14" t="s">
+        <v>46</v>
+      </c>
+      <c r="D14" s="14" t="s">
         <v>18</v>
       </c>
-    </row>
-    <row r="5" spans="1:8">
-      <c r="B5" s="16" t="s">
-        <v>19</v>
-      </c>
-      <c r="C5" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>16</v>
-      </c>
-      <c r="E5" s="16" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="6" spans="1:8">
-      <c r="B6" s="16" t="s">
-        <v>22</v>
-      </c>
-      <c r="C6" s="15" t="s">
-        <v>23</v>
-      </c>
-      <c r="D6" s="16" t="s">
-        <v>24</v>
-      </c>
-      <c r="E6" s="16" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="8" spans="1:8">
-      <c r="A8" s="16" t="s">
-        <v>26</v>
-      </c>
-      <c r="B8" s="16" t="s">
-        <v>27</v>
-      </c>
-      <c r="C8" s="15" t="s">
-        <v>28</v>
-      </c>
-      <c r="D8" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E8" s="16" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:8">
-      <c r="B9" s="16" t="s">
-        <v>30</v>
-      </c>
-      <c r="C9" s="15" t="s">
-        <v>31</v>
-      </c>
-      <c r="D9" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E9" s="16" t="s">
-        <v>32</v>
-      </c>
-    </row>
-    <row r="10" spans="1:8">
-      <c r="B10" s="16" t="s">
-        <v>33</v>
-      </c>
-      <c r="C10" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="D10" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E10" s="16" t="s">
-        <v>35</v>
-      </c>
-    </row>
-    <row r="11" spans="1:8">
-      <c r="B11" s="16" t="s">
-        <v>36</v>
-      </c>
-      <c r="C11" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="D11" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E11" s="16" t="s">
-        <v>38</v>
-      </c>
-    </row>
-    <row r="13" spans="1:8">
-      <c r="A13" s="16" t="s">
-        <v>39</v>
-      </c>
-      <c r="B13" s="16" t="s">
-        <v>40</v>
-      </c>
-      <c r="C13" s="15" t="s">
-        <v>41</v>
-      </c>
-      <c r="D13" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E13" s="16" t="s">
-        <v>42</v>
-      </c>
-    </row>
-    <row r="14" spans="1:8">
-      <c r="B14" s="16" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="15" t="s">
-        <v>44</v>
-      </c>
-      <c r="D14" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E14" s="16" t="s">
-        <v>45</v>
+      <c r="E14" s="5" t="s">
+        <v>47</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="B15" s="16" t="s">
-        <v>46</v>
-      </c>
-      <c r="C15" s="15" t="s">
-        <v>47</v>
-      </c>
-      <c r="D15" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E15" s="16" t="s">
+      <c r="B15" s="5" t="s">
         <v>48</v>
       </c>
+      <c r="C15" s="14" t="s">
+        <v>49</v>
+      </c>
+      <c r="D15" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E15" s="5" t="s">
+        <v>50</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="B16" s="16" t="s">
-        <v>49</v>
-      </c>
-      <c r="C16" s="15" t="s">
-        <v>50</v>
-      </c>
-      <c r="D16" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E16" s="16" t="s">
+      <c r="B16" s="5" t="s">
         <v>51</v>
       </c>
+      <c r="C16" s="14" t="s">
+        <v>52</v>
+      </c>
+      <c r="D16" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E16" s="5" t="s">
+        <v>53</v>
+      </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="B18" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C18" s="16" t="s">
+      <c r="A18" s="5" t="s">
         <v>54</v>
       </c>
-      <c r="E18" s="16" t="s">
+      <c r="B18" s="5" t="s">
         <v>55</v>
       </c>
+      <c r="C18" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E18" s="5" t="s">
+        <v>57</v>
+      </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="5" t="s">
+        <v>58</v>
+      </c>
+      <c r="C19" s="5" t="s">
         <v>56</v>
       </c>
-      <c r="C19" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E19" s="16" t="s">
-        <v>57</v>
+      <c r="E19" s="5" t="s">
+        <v>59</v>
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="B20" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C20" s="15" t="s">
-        <v>59</v>
-      </c>
-      <c r="D20" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E20" s="16" t="s">
+      <c r="B20" s="5" t="s">
         <v>60</v>
       </c>
+      <c r="C20" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E20" s="5" t="s">
+        <v>62</v>
+      </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="B21" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="C21" s="16" t="s">
-        <v>54</v>
-      </c>
-      <c r="E21" s="16" t="s">
-        <v>62</v>
+      <c r="B21" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="C21" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E21" s="5" t="s">
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="16" t="s">
-        <v>63</v>
-      </c>
-      <c r="B23" s="16" t="s">
-        <v>64</v>
-      </c>
-      <c r="C23" s="15" t="s">
+      <c r="A23" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="D23" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E23" s="16" t="s">
+      <c r="B23" s="5" t="s">
         <v>66</v>
       </c>
+      <c r="C23" s="14" t="s">
+        <v>67</v>
+      </c>
+      <c r="D23" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E23" s="5" t="s">
+        <v>68</v>
+      </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="B24" s="16" t="s">
-        <v>67</v>
-      </c>
-      <c r="C24" s="15" t="s">
-        <v>68</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E24" s="16" t="s">
+      <c r="B24" s="5" t="s">
         <v>69</v>
       </c>
+      <c r="C24" s="14" t="s">
+        <v>70</v>
+      </c>
+      <c r="D24" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>71</v>
+      </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="B25" s="16" t="s">
-        <v>70</v>
-      </c>
-      <c r="C25" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>12</v>
-      </c>
-      <c r="E25" s="16" t="s">
+      <c r="B25" s="5" t="s">
         <v>72</v>
       </c>
+      <c r="C25" s="14" t="s">
+        <v>73</v>
+      </c>
+      <c r="D25" s="14" t="s">
+        <v>14</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>74</v>
+      </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="B26" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C26" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>16</v>
-      </c>
-      <c r="E26" s="16" t="s">
+      <c r="B26" s="5" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="6"/>
-      <c r="B28" s="6"/>
-      <c r="C28" s="6"/>
-    </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="6"/>
-      <c r="B29" s="6"/>
-      <c r="C29" s="6"/>
-    </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="6"/>
-      <c r="B30" s="6"/>
-      <c r="C30" s="6"/>
-    </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="6"/>
-      <c r="B31" s="6"/>
-      <c r="C31" s="6"/>
-    </row>
-    <row r="32" spans="1:5">
-      <c r="A32" s="6"/>
-      <c r="B32" s="6"/>
-      <c r="C32" s="6"/>
-    </row>
-    <row r="33" spans="1:3">
-      <c r="A33" s="6"/>
-      <c r="B33" s="6"/>
-      <c r="C33" s="6"/>
+      <c r="C26" s="14" t="s">
+        <v>76</v>
+      </c>
+      <c r="D26" s="14" t="s">
+        <v>18</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>77</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2725,306 +2899,306 @@
   <dimension ref="A1:K22"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20"/>
   <cols>
-    <col min="1" max="1" width="20.5454545454545" style="4" customWidth="1"/>
-    <col min="2" max="2" width="25.8181818181818" style="4" customWidth="1"/>
-    <col min="3" max="3" width="18.1818181818182" style="4" customWidth="1"/>
-    <col min="4" max="4" width="27.8181818181818" style="5" customWidth="1"/>
-    <col min="5" max="5" width="17.6363636363636" style="4" customWidth="1"/>
-    <col min="6" max="7" width="9" style="6"/>
-    <col min="8" max="16384" width="9" style="7"/>
+    <col min="1" max="1" width="20.5454545454545" style="3" customWidth="1"/>
+    <col min="2" max="2" width="25.8181818181818" style="3" customWidth="1"/>
+    <col min="3" max="3" width="18.1818181818182" style="3" customWidth="1"/>
+    <col min="4" max="4" width="27.8181818181818" style="4" customWidth="1"/>
+    <col min="5" max="5" width="17.6363636363636" style="3" customWidth="1"/>
+    <col min="6" max="7" width="9" style="5"/>
+    <col min="8" max="16384" width="9" style="6"/>
   </cols>
   <sheetData>
     <row r="1" ht="21" spans="1:11">
-      <c r="A1" s="4" t="s">
-        <v>76</v>
-      </c>
-      <c r="B1" s="4" t="s">
-        <v>77</v>
-      </c>
-      <c r="C1" s="4" t="s">
+      <c r="A1" s="3" t="s">
         <v>78</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="B1" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="C1" s="3" t="s">
         <v>80</v>
       </c>
+      <c r="D1" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="E1" s="3" t="s">
+        <v>82</v>
+      </c>
     </row>
     <row r="2" ht="21" spans="1:11">
-      <c r="A2" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="B2" s="4" t="s">
-        <v>82</v>
-      </c>
-      <c r="C2" s="4" t="s">
+      <c r="A2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B2" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D2" s="5">
+      <c r="C2" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="7" t="s">
-        <v>84</v>
+      <c r="K2" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="3" ht="21" spans="1:11">
-      <c r="A3" s="4" t="s">
-        <v>85</v>
-      </c>
-      <c r="B3" s="4" t="s">
+      <c r="A3" s="3" t="s">
         <v>86</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="B3" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D3" s="5" t="s">
+      <c r="C3" s="3" t="s">
         <v>88</v>
       </c>
+      <c r="D3" s="4" t="s">
+        <v>89</v>
+      </c>
     </row>
     <row r="4" spans="1:11">
-      <c r="A4" s="4" t="s">
-        <v>89</v>
-      </c>
-      <c r="B4" s="4" t="s">
+      <c r="A4" s="3" t="s">
         <v>90</v>
       </c>
-      <c r="C4" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D4" s="5" t="s">
+      <c r="B4" s="3" t="s">
         <v>91</v>
       </c>
+      <c r="C4" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>92</v>
+      </c>
     </row>
     <row r="5" ht="21" spans="1:11">
-      <c r="A5" s="4" t="s">
-        <v>92</v>
-      </c>
-      <c r="B5" s="4" t="s">
+      <c r="A5" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="B5" s="3" t="s">
         <v>94</v>
       </c>
+      <c r="E5" s="3" t="s">
+        <v>95</v>
+      </c>
     </row>
     <row r="6" ht="21" spans="1:11">
-      <c r="A6" s="4" t="s">
-        <v>95</v>
-      </c>
-      <c r="B6" s="4" t="s">
+      <c r="A6" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="B6" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="C6" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="D6" s="4" t="s">
         <v>99</v>
       </c>
+      <c r="E6" s="3" t="s">
+        <v>100</v>
+      </c>
     </row>
     <row r="7" ht="21" spans="1:11">
-      <c r="A7" s="4" t="s">
+      <c r="A7" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="B7" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D7" s="4" t="s">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="8" ht="21" spans="1:11">
+      <c r="A8" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="B8" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="9" ht="21" spans="1:11">
+      <c r="A9" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="B9" s="3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>109</v>
+      </c>
+    </row>
+    <row r="10" ht="21" spans="1:11">
+      <c r="A10" s="3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B10" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>88</v>
+      </c>
+      <c r="D10" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K10" s="6" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="11" ht="21" spans="1:11">
+      <c r="A11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="B11" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="D11" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E11" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>101</v>
-      </c>
-      <c r="C7" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D7" s="5" t="s">
-        <v>102</v>
-      </c>
-    </row>
-    <row r="8" ht="21" spans="1:11">
-      <c r="A8" s="4" t="s">
-        <v>103</v>
-      </c>
-      <c r="B8" s="4" t="s">
-        <v>104</v>
-      </c>
-      <c r="D8" s="5" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="9" ht="21" spans="1:11">
-      <c r="A9" s="4" t="s">
-        <v>106</v>
-      </c>
-      <c r="B9" s="4" t="s">
-        <v>107</v>
-      </c>
-      <c r="D9" s="5" t="s">
-        <v>108</v>
-      </c>
-    </row>
-    <row r="10" ht="21" spans="1:11">
-      <c r="A10" s="4" t="s">
+      <c r="K11" s="6" t="s">
+        <v>115</v>
+      </c>
+    </row>
+    <row r="12" ht="21" spans="1:11">
+      <c r="A12" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="B12" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="F12" s="9"/>
+    </row>
+    <row r="13" ht="23" customHeight="1" spans="1:11">
+      <c r="A13" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="E13" s="10" t="s">
+        <v>121</v>
+      </c>
+      <c r="G13" s="11"/>
+    </row>
+    <row r="14" ht="21" spans="1:11">
+      <c r="A14" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="B14" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="15" ht="21" spans="1:11">
+      <c r="A15" s="3" t="s">
+        <v>124</v>
+      </c>
+      <c r="B15" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="16" ht="21" spans="1:11">
+      <c r="A16" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="B16" s="3" t="s">
+        <v>128</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>129</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="17" ht="21" spans="1:4">
+      <c r="A17" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="B17" s="3" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="18" ht="21" spans="1:4">
+      <c r="A18" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="B18" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="19" ht="21" spans="1:4">
+      <c r="A19" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="B10" s="4" t="s">
-        <v>109</v>
-      </c>
-      <c r="C10" s="8" t="s">
-        <v>87</v>
-      </c>
-      <c r="D10" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="K10" s="7" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="11" ht="21" spans="1:11">
-      <c r="A11" s="4" t="s">
-        <v>111</v>
-      </c>
-      <c r="B11" s="4" t="s">
-        <v>112</v>
-      </c>
-      <c r="C11" s="4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D11" s="9" t="s">
-        <v>11</v>
-      </c>
-      <c r="E11" s="4" t="s">
-        <v>99</v>
-      </c>
-      <c r="K11" s="7" t="s">
-        <v>114</v>
-      </c>
-    </row>
-    <row r="12" ht="21" spans="1:11">
-      <c r="A12" s="4" t="s">
-        <v>115</v>
-      </c>
-      <c r="B12" s="4" t="s">
-        <v>116</v>
-      </c>
-      <c r="F12" s="10"/>
-    </row>
-    <row r="13" ht="23" customHeight="1" spans="1:11">
-      <c r="A13" s="4" t="s">
-        <v>117</v>
-      </c>
-      <c r="B13" s="4" t="s">
-        <v>118</v>
-      </c>
-      <c r="D13" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="E13" s="11" t="s">
-        <v>120</v>
-      </c>
-      <c r="G13" s="12"/>
-    </row>
-    <row r="14" ht="21" spans="1:11">
-      <c r="A14" s="4" t="s">
-        <v>121</v>
-      </c>
-      <c r="B14" s="4" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="15" ht="21" spans="1:11">
-      <c r="A15" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>124</v>
-      </c>
-      <c r="C15" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="E15" s="4" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="16" ht="21" spans="1:11">
-      <c r="A16" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="B16" s="4" t="s">
-        <v>127</v>
-      </c>
-      <c r="D16" s="5" t="s">
-        <v>128</v>
-      </c>
-      <c r="E16" s="4" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="17" ht="21" spans="1:4">
-      <c r="A17" s="4" t="s">
-        <v>130</v>
-      </c>
-      <c r="B17" s="4" t="s">
-        <v>131</v>
-      </c>
-    </row>
-    <row r="18" ht="21" spans="1:4">
-      <c r="A18" s="4" t="s">
-        <v>132</v>
-      </c>
-      <c r="B18" s="4" t="s">
-        <v>133</v>
-      </c>
-      <c r="C18" s="4" t="s">
-        <v>97</v>
-      </c>
-      <c r="D18" s="5" t="s">
-        <v>98</v>
-      </c>
-    </row>
-    <row r="19" ht="21" spans="1:4">
-      <c r="A19" s="4" t="s">
-        <v>5</v>
-      </c>
-      <c r="B19" s="4" t="s">
-        <v>134</v>
-      </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="14" t="s">
+      <c r="B19" s="3" t="s">
         <v>135</v>
       </c>
+      <c r="C19" s="12"/>
+      <c r="D19" s="13" t="s">
+        <v>136</v>
+      </c>
     </row>
     <row r="20" ht="21" spans="1:4">
-      <c r="A20" s="4" t="s">
+      <c r="A20" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B20" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="21" ht="21" spans="1:4">
+      <c r="A21" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="B20" s="4" t="s">
-        <v>136</v>
-      </c>
-      <c r="D20" s="5" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="21" ht="21" spans="1:4">
-      <c r="A21" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B21" s="4" t="s">
-        <v>137</v>
-      </c>
-      <c r="D21" s="15" t="s">
-        <v>24</v>
+      <c r="B21" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="14" t="s">
+        <v>26</v>
       </c>
     </row>
     <row r="22" ht="21" spans="1:4">
-      <c r="A22" s="4" t="s">
-        <v>138</v>
-      </c>
-      <c r="B22" s="4" t="s">
+      <c r="A22" s="3" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="4" t="s">
-        <v>87</v>
-      </c>
-      <c r="D22" s="5" t="s">
+      <c r="B22" s="3" t="s">
         <v>140</v>
+      </c>
+      <c r="C22" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D22" s="4" t="s">
+        <v>141</v>
       </c>
     </row>
   </sheetData>
@@ -3052,61 +3226,61 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="2" ht="21" spans="1:6">
+      <c r="A2" s="1" t="s">
+        <v>139</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>88</v>
+      </c>
+      <c r="D2" s="1" t="s">
         <v>141</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D1" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="E1" s="2" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="2" ht="21" spans="1:6">
-      <c r="A2" s="3" t="s">
-        <v>138</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C2" s="3" t="s">
-        <v>87</v>
-      </c>
-      <c r="D2" s="3" t="s">
-        <v>140</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
     </row>
     <row r="3" ht="21" spans="1:6">
-      <c r="A3" s="3" t="s">
-        <v>85</v>
+      <c r="A3" s="1" t="s">
+        <v>86</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
     </row>
     <row r="4" ht="21" spans="1:6">
-      <c r="A4" s="3" t="s">
-        <v>151</v>
+      <c r="A4" s="1" t="s">
+        <v>152</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
     </row>
   </sheetData>

--- a/other_files/汇兴-增鑫API数据接入/网关数据.xlsx
+++ b/other_files/汇兴-增鑫API数据接入/网关数据.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="25600" windowHeight="12790"/>
+    <workbookView windowWidth="14830" windowHeight="11090"/>
   </bookViews>
   <sheets>
     <sheet name="栏舍编号" sheetId="1" r:id="rId1"/>
@@ -29,11 +29,11 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="154">
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="171">
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -44,7 +44,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -55,7 +55,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -66,7 +66,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -77,7 +77,7 @@
   <si>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -86,7 +86,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <charset val="134"/>
@@ -95,7 +95,7 @@
     </r>
     <r>
       <rPr>
-        <sz val="11"/>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -104,7 +104,24 @@
     </r>
   </si>
   <si>
-    <t>区域id</t>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>区域</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Arial"/>
+        <charset val="134"/>
+      </rPr>
+      <t>id</t>
+    </r>
   </si>
   <si>
     <t>unitName</t>
@@ -123,17 +140,155 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
+      <t>2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>栋</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2023092836</t>
+  </si>
+  <si>
+    <t>39.165.19.84</t>
+  </si>
+  <si>
+    <t>40a6fc2e64859dad66cf87057c76ad9e</t>
+  </si>
+  <si>
+    <t>281d665ce85c54fb0731ac8bb2d65dd9</t>
+  </si>
+  <si>
+    <r>
+      <t>2-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2023120402</t>
+  </si>
+  <si>
+    <t>47.97.125.216</t>
+  </si>
+  <si>
+    <t>e712a7dd9912b3dd328ebeab531dc543</t>
+  </si>
+  <si>
+    <t>ef5476d0282e28c06eaa25a4b871f388</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>可以共用</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="Arial"/>
         <charset val="134"/>
       </rPr>
-      <t>2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>ip</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>？</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>2-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041507</t>
+  </si>
+  <si>
+    <t>90cba802405352409a87df035cc776b0</t>
+  </si>
+  <si>
+    <t>d58ad1e25f78b096ecabdbe27d43d170</t>
+  </si>
+  <si>
+    <r>
+      <t>2-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="黑体"/>
+        <charset val="134"/>
+      </rPr>
+      <t>单元</t>
+    </r>
+  </si>
+  <si>
+    <t>XH2024041511</t>
+  </si>
+  <si>
+    <t>10.147.0.118</t>
+  </si>
+  <si>
+    <t>41cd1a45d1c5c881e3d110d26258fa00</t>
+  </si>
+  <si>
+    <t>28630f72d983d791baa1caaee8badade</t>
+  </si>
+  <si>
+    <r>
+      <t>3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -143,17 +298,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>3-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -162,27 +311,21 @@
     </r>
   </si>
   <si>
-    <t>XH2023092836</t>
-  </si>
-  <si>
-    <t>39.165.19.84</t>
-  </si>
-  <si>
-    <t>40a6fc2e64859dad66cf87057c76ad9e</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2024090302</t>
+  </si>
+  <si>
+    <t>1cf314e8c706a303cdfce55d0ba8825c</t>
+  </si>
+  <si>
+    <t>89af33006e6e1d52c35ecdf2044d02b9</t>
+  </si>
+  <si>
+    <r>
+      <t>3-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -191,56 +334,21 @@
     </r>
   </si>
   <si>
-    <t>XH2023120402</t>
-  </si>
-  <si>
-    <t>47.97.125.216</t>
-  </si>
-  <si>
-    <t>e712a7dd9912b3dd328ebeab531dc543</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>可以共用</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>ip</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>？</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2023120448</t>
+  </si>
+  <si>
+    <t>1c5072528e1efc9e7d4b68503fd52704</t>
+  </si>
+  <si>
+    <t>9bb8187a403a4d3ed61ff3bc039c44be</t>
+  </si>
+  <si>
+    <r>
+      <t>3-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -249,24 +357,21 @@
     </r>
   </si>
   <si>
-    <t>XH2024041507</t>
-  </si>
-  <si>
-    <t>90cba802405352409a87df035cc776b0</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>2-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2024041504</t>
+  </si>
+  <si>
+    <t>e838146c63828cce106a4983ef93aee8</t>
+  </si>
+  <si>
+    <t>f74dab2dc90e5948d0e507f13df6ad3d</t>
+  </si>
+  <si>
+    <r>
+      <t>3-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -275,27 +380,21 @@
     </r>
   </si>
   <si>
-    <t>XH2024041511</t>
-  </si>
-  <si>
-    <t>10.147.0.118</t>
-  </si>
-  <si>
-    <t>41cd1a45d1c5c881e3d110d26258fa00</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2024041509</t>
+  </si>
+  <si>
+    <t>86ff056dd242c133ca7173a07f53333d</t>
+  </si>
+  <si>
+    <t>88c6d3a266600fd92eeed1f4a5b7907d</t>
+  </si>
+  <si>
+    <r>
+      <t>4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -305,17 +404,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>4-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -324,24 +417,21 @@
     </r>
   </si>
   <si>
-    <t>XH2024090302</t>
-  </si>
-  <si>
-    <t>1cf314e8c706a303cdfce55d0ba8825c</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2024041508</t>
+  </si>
+  <si>
+    <t>4b4469efe50237d4207d60f79b1a56aa</t>
+  </si>
+  <si>
+    <t>e900e03b1d2b6e53fdc708efd3db654e</t>
+  </si>
+  <si>
+    <r>
+      <t>4-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -350,24 +440,21 @@
     </r>
   </si>
   <si>
-    <t>XH2023120448</t>
-  </si>
-  <si>
-    <t>1c5072528e1efc9e7d4b68503fd52704</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2024041502</t>
+  </si>
+  <si>
+    <t>551b9bdc9a95fa2a4c2d1fb924aa4859</t>
+  </si>
+  <si>
+    <t>367643b5cfe7e34ef825220fba636ca5</t>
+  </si>
+  <si>
+    <r>
+      <t>4-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -376,24 +463,21 @@
     </r>
   </si>
   <si>
-    <t>XH2024041504</t>
-  </si>
-  <si>
-    <t>e838146c63828cce106a4983ef93aee8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>3-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2024041505</t>
+  </si>
+  <si>
+    <t>eb0f5c4d9a5b397ff30b0d1f7f2d0100</t>
+  </si>
+  <si>
+    <t>b1590dc13b35c52d5bd55e7e17026d49</t>
+  </si>
+  <si>
+    <r>
+      <t>4-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -402,24 +486,21 @@
     </r>
   </si>
   <si>
-    <t>XH2024041509</t>
-  </si>
-  <si>
-    <t>86ff056dd242c133ca7173a07f53333d</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2024041506</t>
+  </si>
+  <si>
+    <t>e65f1ebafe2787cec95df5e685a511d9</t>
+  </si>
+  <si>
+    <t>9e70d5ed9483e1e4b7a5654b27b6f647</t>
+  </si>
+  <si>
+    <r>
+      <t>5</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -429,17 +510,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>5-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -448,24 +523,18 @@
     </r>
   </si>
   <si>
-    <t>XH2024041508</t>
-  </si>
-  <si>
-    <t>4b4469efe50237d4207d60f79b1a56aa</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>/</t>
+  </si>
+  <si>
+    <t>10c42ed81b5f40cfbc568f35dbae4a8e</t>
+  </si>
+  <si>
+    <r>
+      <t>5-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -474,24 +543,15 @@
     </r>
   </si>
   <si>
-    <t>XH2024041502</t>
-  </si>
-  <si>
-    <t>551b9bdc9a95fa2a4c2d1fb924aa4859</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>d537e9b2b5634e898908f02025df0e6a</t>
+  </si>
+  <si>
+    <r>
+      <t>5-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -500,24 +560,21 @@
     </r>
   </si>
   <si>
-    <t>XH2024041505</t>
-  </si>
-  <si>
-    <t>eb0f5c4d9a5b397ff30b0d1f7f2d0100</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>4-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2024041503</t>
+  </si>
+  <si>
+    <t>8a1b5538dd9e0266c60d32b3d2f5a50b</t>
+  </si>
+  <si>
+    <t>848461992bca04cd3e2794967753a87f</t>
+  </si>
+  <si>
+    <r>
+      <t>5-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -526,24 +583,15 @@
     </r>
   </si>
   <si>
-    <t>XH2024041506</t>
-  </si>
-  <si>
-    <t>e65f1ebafe2787cec95df5e685a511d9</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>7c44240126a240c087f91a0890fba4f8</t>
+  </si>
+  <si>
+    <r>
+      <t>6</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -553,17 +601,11 @@
   </si>
   <si>
     <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+      <t>6-1</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -572,24 +614,21 @@
     </r>
   </si>
   <si>
-    <t>/</t>
-  </si>
-  <si>
-    <t>10c42ed81b5f40cfbc568f35dbae4a8e</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2023120430</t>
+  </si>
+  <si>
+    <t>41c897cadfa52eeaf42149ff2b550daa</t>
+  </si>
+  <si>
+    <t>43984addeac090ab612aa7043fdd3c0a</t>
+  </si>
+  <si>
+    <r>
+      <t>6-2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -598,21 +637,21 @@
     </r>
   </si>
   <si>
-    <t>d537e9b2b5634e898908f02025df0e6a</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2025102103</t>
+  </si>
+  <si>
+    <t>64ba729f187eabcf1ae4b6d66f96145e</t>
+  </si>
+  <si>
+    <t>a9c4a605ba08315e4e3fbafb66b94b28</t>
+  </si>
+  <si>
+    <r>
+      <t>6-3</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -621,24 +660,21 @@
     </r>
   </si>
   <si>
-    <t>XH2024041503</t>
-  </si>
-  <si>
-    <t>8a1b5538dd9e0266c60d32b3d2f5a50b</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>5-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
+    <t>XH2023120447</t>
+  </si>
+  <si>
+    <t>0099d2a09dbc98294ab356c8dc8f52f3</t>
+  </si>
+  <si>
+    <t>6f59f9702cc0719bdae862477bb1ccd0</t>
+  </si>
+  <si>
+    <r>
+      <t>6-4</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
         <color theme="1"/>
         <rFont val="黑体"/>
         <charset val="134"/>
@@ -647,131 +683,13 @@
     </r>
   </si>
   <si>
-    <t>7c44240126a240c087f91a0890fba4f8</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>栋</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6-1</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2023120430</t>
-  </si>
-  <si>
-    <t>41c897cadfa52eeaf42149ff2b550daa</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2025102103</t>
-  </si>
-  <si>
-    <t>64ba729f187eabcf1ae4b6d66f96145e</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6-3</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
-    <t>XH2023120447</t>
-  </si>
-  <si>
-    <t>0099d2a09dbc98294ab356c8dc8f52f3</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Arial"/>
-        <charset val="134"/>
-      </rPr>
-      <t>6-4</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="黑体"/>
-        <charset val="134"/>
-      </rPr>
-      <t>单元</t>
-    </r>
-  </si>
-  <si>
     <t>XH2024081602</t>
   </si>
   <si>
     <t>b667fb650620892a4d67ebe8ac8dc9a8</t>
+  </si>
+  <si>
+    <t>8a84d0103ff885900c130e1420f66fdf</t>
   </si>
   <si>
     <r>
@@ -1526,7 +1444,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="30">
+  <fonts count="31">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1569,9 +1487,15 @@
       <charset val="134"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="12"/>
       <color theme="1"/>
-      <name val="宋体"/>
+      <name val="Arial"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF0E1E21"/>
+      <name val="Arial"/>
       <charset val="134"/>
     </font>
     <font>
@@ -1719,18 +1643,18 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="11"/>
+      <sz val="16"/>
+      <name val="黑体"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="12"/>
       <color theme="1"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="黑体"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="16"/>
       <name val="黑体"/>
       <charset val="134"/>
     </font>
@@ -2055,137 +1979,137 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="2">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="2">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="3" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="4" borderId="5">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="4" borderId="4">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="5" borderId="6">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="6" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="11" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="13" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="14" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="15" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="16" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="17" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="18" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="19" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="20" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="21" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="22" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="23" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="24" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="25" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="26" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="27" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="28" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="29" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="30" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="31" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="32" borderId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="2">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="3">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="3" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="4" borderId="5">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="4" borderId="4">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="5" borderId="6">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="6" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="7" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="11" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="12" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="13" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="14" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="15" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="16" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="17" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="18" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="19" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="20" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="21" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="22" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="23" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="24" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="25" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="26" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="27" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="28" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="29" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="30" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="31" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
@@ -2234,7 +2158,13 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -2549,31 +2479,31 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:H26"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" outlineLevelCol="7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15.5" outlineLevelCol="7"/>
   <cols>
-    <col min="1" max="1" width="6.81818181818182" style="5" customWidth="1"/>
-    <col min="2" max="2" width="12" style="5" customWidth="1"/>
-    <col min="3" max="3" width="15.9090909090909" style="5" customWidth="1"/>
-    <col min="4" max="4" width="15.6363636363636" style="5" customWidth="1"/>
-    <col min="5" max="5" width="34.5454545454545" style="5" customWidth="1"/>
-    <col min="6" max="6" width="25.0909090909091" style="5" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="5"/>
+    <col min="1" max="1" width="6.81818181818182" style="15" customWidth="1"/>
+    <col min="2" max="2" width="12" style="15" customWidth="1"/>
+    <col min="3" max="3" width="15.9090909090909" style="15" customWidth="1"/>
+    <col min="4" max="4" width="15.6363636363636" style="15" customWidth="1"/>
+    <col min="5" max="5" width="13.3636363636364" style="15" customWidth="1"/>
+    <col min="6" max="6" width="25.0909090909091" style="15" customWidth="1"/>
+    <col min="7" max="16384" width="9" style="15"/>
   </cols>
   <sheetData>
-    <row r="1" s="5" customFormat="1" spans="1:8">
-      <c r="A1" s="5" t="s">
+    <row r="1" s="15" customFormat="1" spans="1:8">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="5" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="5" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="5" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="5" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
       <c r="F1" s="15" t="s">
@@ -2581,309 +2511,360 @@
       </c>
     </row>
     <row r="2" spans="1:8">
-      <c r="B2" s="5" t="s">
+      <c r="B2" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="C2" s="14" t="s">
+      <c r="C2" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="15" t="s">
         <v>8</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="15" t="s">
         <v>9</v>
       </c>
-      <c r="F2" s="5" t="s">
+      <c r="F2" s="15" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:8">
-      <c r="A3" s="5" t="s">
+      <c r="A3" s="15" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" s="15" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="14" t="s">
+      <c r="C3" s="16" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="14" t="s">
+      <c r="D3" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E3" s="5" t="s">
+      <c r="E3" s="15" t="s">
         <v>15</v>
       </c>
+      <c r="F3" s="17" t="s">
+        <v>16</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
-      <c r="B4" s="5" t="s">
-        <v>16</v>
-      </c>
-      <c r="C4" s="14" t="s">
+      <c r="B4" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="D4" s="16" t="s">
+      <c r="C4" s="16" t="s">
         <v>18</v>
       </c>
-      <c r="E4" s="5" t="s">
+      <c r="D4" s="18" t="s">
         <v>19</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="E4" s="15" t="s">
         <v>20</v>
       </c>
+      <c r="F4" s="17" t="s">
+        <v>21</v>
+      </c>
+      <c r="H4" s="15" t="s">
+        <v>22</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
-      <c r="B5" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="C5" s="14" t="s">
-        <v>22</v>
-      </c>
-      <c r="D5" s="16" t="s">
-        <v>18</v>
-      </c>
-      <c r="E5" s="5" t="s">
+      <c r="B5" s="15" t="s">
         <v>23</v>
       </c>
+      <c r="C5" s="16" t="s">
+        <v>24</v>
+      </c>
+      <c r="D5" s="18" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="15" t="s">
+        <v>25</v>
+      </c>
+      <c r="F5" s="17" t="s">
+        <v>26</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
-      <c r="B6" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="C6" s="14" t="s">
-        <v>25</v>
-      </c>
-      <c r="D6" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="E6" s="5" t="s">
+      <c r="B6" s="15" t="s">
         <v>27</v>
       </c>
+      <c r="C6" s="16" t="s">
+        <v>28</v>
+      </c>
+      <c r="D6" s="15" t="s">
+        <v>29</v>
+      </c>
+      <c r="E6" s="15" t="s">
+        <v>30</v>
+      </c>
+      <c r="F6" s="17" t="s">
+        <v>31</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
-      <c r="A8" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="C8" s="14" t="s">
-        <v>30</v>
-      </c>
-      <c r="D8" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E8" s="5" t="s">
-        <v>31</v>
+      <c r="A8" s="15" t="s">
+        <v>32</v>
+      </c>
+      <c r="B8" s="15" t="s">
+        <v>33</v>
+      </c>
+      <c r="C8" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="15" t="s">
+        <v>35</v>
+      </c>
+      <c r="F8" s="17" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:8">
-      <c r="B9" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C9" s="14" t="s">
-        <v>33</v>
-      </c>
-      <c r="D9" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E9" s="5" t="s">
-        <v>34</v>
+      <c r="B9" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="C9" s="16" t="s">
+        <v>38</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="15" t="s">
+        <v>39</v>
+      </c>
+      <c r="F9" s="17" t="s">
+        <v>40</v>
       </c>
     </row>
     <row r="10" spans="1:8">
-      <c r="B10" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="C10" s="14" t="s">
-        <v>36</v>
-      </c>
-      <c r="D10" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E10" s="5" t="s">
-        <v>37</v>
+      <c r="B10" s="15" t="s">
+        <v>41</v>
+      </c>
+      <c r="C10" s="16" t="s">
+        <v>42</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="15" t="s">
+        <v>43</v>
+      </c>
+      <c r="F10" s="17" t="s">
+        <v>44</v>
       </c>
     </row>
     <row r="11" spans="1:8">
-      <c r="B11" s="5" t="s">
-        <v>38</v>
-      </c>
-      <c r="C11" s="14" t="s">
-        <v>39</v>
-      </c>
-      <c r="D11" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="5" t="s">
-        <v>40</v>
+      <c r="B11" s="15" t="s">
+        <v>45</v>
+      </c>
+      <c r="C11" s="16" t="s">
+        <v>46</v>
+      </c>
+      <c r="D11" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="15" t="s">
+        <v>47</v>
+      </c>
+      <c r="F11" s="17" t="s">
+        <v>48</v>
       </c>
     </row>
     <row r="13" spans="1:8">
-      <c r="A13" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="B13" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="C13" s="14" t="s">
-        <v>43</v>
-      </c>
-      <c r="D13" s="14" t="s">
+      <c r="A13" s="15" t="s">
+        <v>49</v>
+      </c>
+      <c r="B13" s="15" t="s">
+        <v>50</v>
+      </c>
+      <c r="C13" s="16" t="s">
+        <v>51</v>
+      </c>
+      <c r="D13" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E13" s="5" t="s">
-        <v>44</v>
+      <c r="E13" s="15" t="s">
+        <v>52</v>
+      </c>
+      <c r="F13" s="17" t="s">
+        <v>53</v>
       </c>
     </row>
     <row r="14" spans="1:8">
-      <c r="B14" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="C14" s="14" t="s">
-        <v>46</v>
-      </c>
-      <c r="D14" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E14" s="5" t="s">
-        <v>47</v>
+      <c r="B14" s="15" t="s">
+        <v>54</v>
+      </c>
+      <c r="C14" s="16" t="s">
+        <v>55</v>
+      </c>
+      <c r="D14" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="15" t="s">
+        <v>56</v>
+      </c>
+      <c r="F14" s="17" t="s">
+        <v>57</v>
       </c>
     </row>
     <row r="15" spans="1:8">
-      <c r="B15" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="C15" s="14" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E15" s="5" t="s">
-        <v>50</v>
+      <c r="B15" s="15" t="s">
+        <v>58</v>
+      </c>
+      <c r="C15" s="16" t="s">
+        <v>59</v>
+      </c>
+      <c r="D15" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F15" s="17" t="s">
+        <v>61</v>
       </c>
     </row>
     <row r="16" spans="1:8">
-      <c r="B16" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="C16" s="14" t="s">
-        <v>52</v>
-      </c>
-      <c r="D16" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E16" s="5" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B18" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="C18" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E18" s="5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="B19" s="5" t="s">
-        <v>58</v>
-      </c>
-      <c r="C19" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E19" s="5" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="B20" s="5" t="s">
-        <v>60</v>
-      </c>
-      <c r="C20" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="D20" s="14" t="s">
+      <c r="B16" s="15" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="16" t="s">
+        <v>63</v>
+      </c>
+      <c r="D16" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="15" t="s">
+        <v>64</v>
+      </c>
+      <c r="F16" s="17" t="s">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6">
+      <c r="A18" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="B18" s="15" t="s">
+        <v>67</v>
+      </c>
+      <c r="C18" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E18" s="15" t="s">
+        <v>69</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6">
+      <c r="B19" s="15" t="s">
+        <v>70</v>
+      </c>
+      <c r="C19" s="15" t="s">
+        <v>68</v>
+      </c>
+      <c r="E19" s="15" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6">
+      <c r="B20" s="15" t="s">
+        <v>72</v>
+      </c>
+      <c r="C20" s="16" t="s">
+        <v>73</v>
+      </c>
+      <c r="D20" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E20" s="5" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="B21" s="5" t="s">
-        <v>63</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>65</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="C23" s="14" t="s">
-        <v>67</v>
-      </c>
-      <c r="D23" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E23" s="5" t="s">
+      <c r="E20" s="15" t="s">
+        <v>74</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>75</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6">
+      <c r="B21" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="C21" s="15" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="B24" s="5" t="s">
-        <v>69</v>
-      </c>
-      <c r="C24" s="14" t="s">
-        <v>70</v>
-      </c>
-      <c r="D24" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E24" s="5" t="s">
-        <v>71</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="B25" s="5" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="14" t="s">
-        <v>73</v>
-      </c>
-      <c r="D25" s="14" t="s">
+      <c r="E21" s="15" t="s">
+        <v>77</v>
+      </c>
+    </row>
+    <row r="23" spans="1:6">
+      <c r="A23" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="B23" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="C23" s="16" t="s">
+        <v>80</v>
+      </c>
+      <c r="D23" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E23" s="15" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="17" t="s">
+        <v>82</v>
+      </c>
+    </row>
+    <row r="24" spans="1:6">
+      <c r="B24" s="15" t="s">
+        <v>83</v>
+      </c>
+      <c r="C24" s="16" t="s">
+        <v>84</v>
+      </c>
+      <c r="D24" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E24" s="15" t="s">
+        <v>85</v>
+      </c>
+      <c r="F24" s="17" t="s">
+        <v>86</v>
+      </c>
+    </row>
+    <row r="25" spans="1:6">
+      <c r="B25" s="15" t="s">
+        <v>87</v>
+      </c>
+      <c r="C25" s="16" t="s">
+        <v>88</v>
+      </c>
+      <c r="D25" s="16" t="s">
         <v>14</v>
       </c>
-      <c r="E25" s="5" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="B26" s="5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C26" s="14" t="s">
-        <v>76</v>
-      </c>
-      <c r="D26" s="14" t="s">
-        <v>18</v>
-      </c>
-      <c r="E26" s="5" t="s">
-        <v>77</v>
+      <c r="E25" s="15" t="s">
+        <v>89</v>
+      </c>
+      <c r="F25" s="17" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6">
+      <c r="B26" s="15" t="s">
+        <v>91</v>
+      </c>
+      <c r="C26" s="16" t="s">
+        <v>92</v>
+      </c>
+      <c r="D26" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="E26" s="15" t="s">
+        <v>93</v>
+      </c>
+      <c r="F26" s="17" t="s">
+        <v>94</v>
       </c>
     </row>
   </sheetData>
@@ -2910,19 +2891,19 @@
   <sheetData>
     <row r="1" ht="21" spans="1:11">
       <c r="A1" s="3" t="s">
-        <v>78</v>
+        <v>95</v>
       </c>
       <c r="B1" s="3" t="s">
-        <v>79</v>
+        <v>96</v>
       </c>
       <c r="C1" s="3" t="s">
-        <v>80</v>
+        <v>97</v>
       </c>
       <c r="D1" s="4" t="s">
-        <v>81</v>
+        <v>98</v>
       </c>
       <c r="E1" s="3" t="s">
-        <v>82</v>
+        <v>99</v>
       </c>
     </row>
     <row r="2" ht="21" spans="1:11">
@@ -2930,108 +2911,108 @@
         <v>10</v>
       </c>
       <c r="B2" s="3" t="s">
-        <v>83</v>
+        <v>100</v>
       </c>
       <c r="C2" s="3" t="s">
-        <v>84</v>
+        <v>101</v>
       </c>
       <c r="D2" s="4">
         <v>1</v>
       </c>
       <c r="K2" s="6" t="s">
-        <v>85</v>
+        <v>102</v>
       </c>
     </row>
     <row r="3" ht="21" spans="1:11">
       <c r="A3" s="3" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B3" s="3" t="s">
-        <v>87</v>
+        <v>104</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D3" s="4" t="s">
-        <v>89</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:11">
       <c r="A4" s="3" t="s">
-        <v>90</v>
+        <v>107</v>
       </c>
       <c r="B4" s="3" t="s">
-        <v>91</v>
+        <v>108</v>
       </c>
       <c r="C4" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D4" s="4" t="s">
-        <v>92</v>
+        <v>109</v>
       </c>
     </row>
     <row r="5" ht="21" spans="1:11">
       <c r="A5" s="3" t="s">
-        <v>93</v>
+        <v>110</v>
       </c>
       <c r="B5" s="3" t="s">
-        <v>94</v>
+        <v>111</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>95</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" ht="21" spans="1:11">
       <c r="A6" s="3" t="s">
-        <v>96</v>
+        <v>113</v>
       </c>
       <c r="B6" s="3" t="s">
-        <v>97</v>
+        <v>114</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D6" s="4" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
     </row>
     <row r="7" ht="21" spans="1:11">
       <c r="A7" s="3" t="s">
-        <v>101</v>
+        <v>118</v>
       </c>
       <c r="B7" s="3" t="s">
-        <v>102</v>
+        <v>119</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D7" s="4" t="s">
-        <v>103</v>
+        <v>120</v>
       </c>
     </row>
     <row r="8" ht="21" spans="1:11">
       <c r="A8" s="3" t="s">
-        <v>104</v>
+        <v>121</v>
       </c>
       <c r="B8" s="3" t="s">
-        <v>105</v>
+        <v>122</v>
       </c>
       <c r="D8" s="4" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" ht="21" spans="1:11">
       <c r="A9" s="3" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B9" s="3" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="D9" s="4" t="s">
-        <v>109</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10" ht="21" spans="1:11">
@@ -3039,118 +3020,118 @@
         <v>7</v>
       </c>
       <c r="B10" s="3" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="C10" s="7" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D10" s="8" t="s">
         <v>13</v>
       </c>
       <c r="K10" s="6" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
     </row>
     <row r="11" ht="21" spans="1:11">
       <c r="A11" s="3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B11" s="3" t="s">
-        <v>113</v>
+        <v>130</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>114</v>
+        <v>131</v>
       </c>
       <c r="D11" s="8" t="s">
         <v>13</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>100</v>
+        <v>117</v>
       </c>
       <c r="K11" s="6" t="s">
-        <v>115</v>
+        <v>132</v>
       </c>
     </row>
     <row r="12" ht="21" spans="1:11">
       <c r="A12" s="3" t="s">
-        <v>116</v>
+        <v>133</v>
       </c>
       <c r="B12" s="3" t="s">
-        <v>117</v>
+        <v>134</v>
       </c>
       <c r="F12" s="9"/>
     </row>
     <row r="13" ht="23" customHeight="1" spans="1:11">
       <c r="A13" s="3" t="s">
-        <v>118</v>
+        <v>135</v>
       </c>
       <c r="B13" s="3" t="s">
-        <v>119</v>
+        <v>136</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>120</v>
+        <v>137</v>
       </c>
       <c r="E13" s="10" t="s">
-        <v>121</v>
+        <v>138</v>
       </c>
       <c r="G13" s="11"/>
     </row>
     <row r="14" ht="21" spans="1:11">
       <c r="A14" s="3" t="s">
-        <v>122</v>
+        <v>139</v>
       </c>
       <c r="B14" s="3" t="s">
-        <v>123</v>
+        <v>140</v>
       </c>
     </row>
     <row r="15" ht="21" spans="1:11">
       <c r="A15" s="3" t="s">
-        <v>124</v>
+        <v>141</v>
       </c>
       <c r="B15" s="3" t="s">
-        <v>125</v>
+        <v>142</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>126</v>
+        <v>143</v>
       </c>
     </row>
     <row r="16" ht="21" spans="1:11">
       <c r="A16" s="3" t="s">
-        <v>127</v>
+        <v>144</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>128</v>
+        <v>145</v>
       </c>
       <c r="D16" s="4" t="s">
-        <v>129</v>
+        <v>146</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>130</v>
+        <v>147</v>
       </c>
     </row>
     <row r="17" ht="21" spans="1:4">
       <c r="A17" s="3" t="s">
-        <v>131</v>
+        <v>148</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>132</v>
+        <v>149</v>
       </c>
     </row>
     <row r="18" ht="21" spans="1:4">
       <c r="A18" s="3" t="s">
-        <v>133</v>
+        <v>150</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>134</v>
+        <v>151</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>98</v>
+        <v>115</v>
       </c>
       <c r="D18" s="4" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
     </row>
     <row r="19" ht="21" spans="1:4">
@@ -3158,11 +3139,11 @@
         <v>6</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>135</v>
+        <v>152</v>
       </c>
       <c r="C19" s="12"/>
       <c r="D19" s="13" t="s">
-        <v>136</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20" ht="21" spans="1:4">
@@ -3170,10 +3151,10 @@
         <v>9</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>137</v>
+        <v>154</v>
       </c>
       <c r="D20" s="4" t="s">
-        <v>27</v>
+        <v>30</v>
       </c>
     </row>
     <row r="21" ht="21" spans="1:4">
@@ -3181,24 +3162,24 @@
         <v>8</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>138</v>
+        <v>155</v>
       </c>
       <c r="D21" s="14" t="s">
-        <v>26</v>
+        <v>29</v>
       </c>
     </row>
     <row r="22" ht="21" spans="1:4">
       <c r="A22" s="3" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>140</v>
+        <v>157</v>
       </c>
       <c r="C22" s="3" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D22" s="4" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
     </row>
   </sheetData>
@@ -3226,61 +3207,61 @@
   <sheetData>
     <row r="1" ht="21" spans="1:6">
       <c r="A1" s="2" t="s">
-        <v>142</v>
+        <v>159</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>143</v>
+        <v>160</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>144</v>
+        <v>161</v>
       </c>
       <c r="D1" s="2" t="s">
-        <v>145</v>
+        <v>162</v>
       </c>
       <c r="E1" s="2" t="s">
-        <v>146</v>
+        <v>163</v>
       </c>
     </row>
     <row r="2" ht="21" spans="1:6">
       <c r="A2" s="1" t="s">
-        <v>139</v>
+        <v>156</v>
       </c>
       <c r="B2" s="2" t="s">
-        <v>147</v>
+        <v>164</v>
       </c>
       <c r="C2" s="1" t="s">
-        <v>88</v>
+        <v>105</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>141</v>
+        <v>158</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>148</v>
+        <v>165</v>
       </c>
       <c r="F2" s="2" t="s">
-        <v>149</v>
+        <v>166</v>
       </c>
     </row>
     <row r="3" ht="21" spans="1:6">
       <c r="A3" s="1" t="s">
-        <v>86</v>
+        <v>103</v>
       </c>
       <c r="B3" s="2" t="s">
-        <v>150</v>
+        <v>167</v>
       </c>
       <c r="D3" s="1">
         <v>1</v>
       </c>
       <c r="E3" s="2" t="s">
-        <v>151</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" ht="21" spans="1:6">
       <c r="A4" s="1" t="s">
-        <v>152</v>
+        <v>169</v>
       </c>
       <c r="B4" s="2" t="s">
-        <v>153</v>
+        <v>170</v>
       </c>
     </row>
   </sheetData>
